--- a/notebooks/MAS_results.xlsx
+++ b/notebooks/MAS_results.xlsx
@@ -628,16 +628,16 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -723,10 +723,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>4.944</v>
+        <v>5</v>
       </c>
       <c r="U3" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V3" t="n">
         <v>5</v>
@@ -818,16 +818,16 @@
         <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>4.778</v>
+        <v>4.944</v>
       </c>
       <c r="U4" t="n">
-        <v>4.667</v>
+        <v>4.833</v>
       </c>
       <c r="V4" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -913,16 +913,16 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
+        <v>4.889</v>
+      </c>
+      <c r="U5" t="n">
         <v>4.833</v>
-      </c>
-      <c r="U5" t="n">
-        <v>5</v>
       </c>
       <c r="V5" t="n">
         <v>4.833</v>
       </c>
       <c r="W5" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -1008,16 +1008,16 @@
         <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>4.944</v>
+        <v>4.889</v>
       </c>
       <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
         <v>4.833</v>
       </c>
-      <c r="V6" t="n">
-        <v>5</v>
-      </c>
       <c r="W6" t="n">
-        <v>5</v>
+        <v>4.833</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -1103,16 +1103,16 @@
         <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>4.833</v>
+        <v>4.778</v>
       </c>
       <c r="U7" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V7" t="n">
-        <v>4.833</v>
+        <v>4.333</v>
       </c>
       <c r="W7" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1198,10 +1198,10 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>4.944</v>
+        <v>5</v>
       </c>
       <c r="U8" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
         <v>5</v>
@@ -1293,16 +1293,16 @@
         <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>4.833</v>
+        <v>4.722</v>
       </c>
       <c r="U9" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V9" t="n">
         <v>4.833</v>
       </c>
       <c r="W9" t="n">
-        <v>4.833</v>
+        <v>4.333</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1388,7 +1388,7 @@
         <v>2</v>
       </c>
       <c r="T10" t="n">
-        <v>4.944</v>
+        <v>5</v>
       </c>
       <c r="U10" t="n">
         <v>5</v>
@@ -1397,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="W10" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1578,13 +1578,13 @@
         <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>4.889</v>
+        <v>4.778</v>
       </c>
       <c r="U12" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="V12" t="n">
-        <v>5</v>
+        <v>4.333</v>
       </c>
       <c r="W12" t="n">
         <v>5</v>
@@ -1673,16 +1673,16 @@
         <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>4.556</v>
+        <v>4.833</v>
       </c>
       <c r="U13" t="n">
-        <v>4.167</v>
+        <v>5</v>
       </c>
       <c r="V13" t="n">
-        <v>4.833</v>
+        <v>4.5</v>
       </c>
       <c r="W13" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1768,16 +1768,16 @@
         <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="U14" t="n">
         <v>5</v>
       </c>
       <c r="V14" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="W14" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>4.722</v>
+        <v>5</v>
       </c>
       <c r="U15" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V15" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>4</v>
       </c>
       <c r="T16" t="n">
+        <v>4.944</v>
+      </c>
+      <c r="U16" t="n">
         <v>4.833</v>
       </c>
-      <c r="U16" t="n">
-        <v>5</v>
-      </c>
       <c r="V16" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W16" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -2056,13 +2056,13 @@
         <v>4.778</v>
       </c>
       <c r="U17" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="V17" t="n">
-        <v>4.833</v>
+        <v>4.333</v>
       </c>
       <c r="W17" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2148,13 +2148,13 @@
         <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>4.944</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
         <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
         <v>5</v>
@@ -2243,16 +2243,16 @@
         <v>2</v>
       </c>
       <c r="T19" t="n">
-        <v>4.722</v>
+        <v>4.889</v>
       </c>
       <c r="U19" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" t="n">
         <v>4.833</v>
       </c>
-      <c r="V19" t="n">
-        <v>4.333</v>
-      </c>
       <c r="W19" t="n">
-        <v>5</v>
+        <v>4.833</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2338,16 +2338,16 @@
         <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>4.833</v>
+        <v>4.667</v>
       </c>
       <c r="U20" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>4.833</v>
+        <v>4</v>
       </c>
       <c r="W20" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2433,16 +2433,16 @@
         <v>1</v>
       </c>
       <c r="T21" t="n">
-        <v>4.833</v>
+        <v>4.944</v>
       </c>
       <c r="U21" t="n">
         <v>4.833</v>
       </c>
       <c r="V21" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W21" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2528,13 +2528,13 @@
         <v>4</v>
       </c>
       <c r="T22" t="n">
-        <v>4.389</v>
+        <v>4.833</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>4.667</v>
       </c>
       <c r="V22" t="n">
-        <v>4.333</v>
+        <v>5</v>
       </c>
       <c r="W22" t="n">
         <v>4.833</v>
@@ -2623,16 +2623,16 @@
         <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>4.389</v>
+        <v>4.778</v>
       </c>
       <c r="U23" t="n">
-        <v>4.667</v>
+        <v>4.333</v>
       </c>
       <c r="V23" t="n">
-        <v>3.833</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="X23" t="n">
         <v>0.5</v>
@@ -2718,16 +2718,16 @@
         <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>4.333</v>
+        <v>4.5</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5</v>
+        <v>4.667</v>
       </c>
       <c r="V24" t="n">
-        <v>4.333</v>
+        <v>4</v>
       </c>
       <c r="W24" t="n">
-        <v>4.167</v>
+        <v>4.833</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2813,16 +2813,16 @@
         <v>3</v>
       </c>
       <c r="T25" t="n">
+        <v>4.889</v>
+      </c>
+      <c r="U25" t="n">
         <v>4.667</v>
       </c>
-      <c r="U25" t="n">
-        <v>4.5</v>
-      </c>
       <c r="V25" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="W25" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2908,16 +2908,16 @@
         <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>4.333</v>
+        <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="V26" t="n">
-        <v>4.333</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -3003,13 +3003,13 @@
         <v>2</v>
       </c>
       <c r="T27" t="n">
-        <v>4.778</v>
+        <v>5</v>
       </c>
       <c r="U27" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="V27" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
         <v>5</v>
@@ -3098,16 +3098,16 @@
         <v>2</v>
       </c>
       <c r="T28" t="n">
-        <v>4.611</v>
+        <v>4.778</v>
       </c>
       <c r="U28" t="n">
-        <v>4.333</v>
+        <v>4.833</v>
       </c>
       <c r="V28" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="W28" t="n">
         <v>4.833</v>
-      </c>
-      <c r="W28" t="n">
-        <v>4.667</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -3193,10 +3193,10 @@
         <v>2</v>
       </c>
       <c r="T29" t="n">
-        <v>4.556</v>
+        <v>4.445</v>
       </c>
       <c r="U29" t="n">
-        <v>4.333</v>
+        <v>4</v>
       </c>
       <c r="V29" t="n">
         <v>4.667</v>
@@ -3288,16 +3288,16 @@
         <v>2</v>
       </c>
       <c r="T30" t="n">
+        <v>4.611</v>
+      </c>
+      <c r="U30" t="n">
         <v>4.833</v>
       </c>
-      <c r="U30" t="n">
-        <v>5</v>
-      </c>
       <c r="V30" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>4.833</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -3383,16 +3383,16 @@
         <v>2</v>
       </c>
       <c r="T31" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="U31" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W31" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3478,16 +3478,16 @@
         <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="U32" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V32" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W32" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -3573,16 +3573,16 @@
         <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>4.833</v>
+        <v>4.778</v>
       </c>
       <c r="U33" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="V33" t="n">
         <v>5</v>
       </c>
       <c r="W33" t="n">
-        <v>4.833</v>
+        <v>4.333</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3668,16 +3668,16 @@
         <v>4</v>
       </c>
       <c r="T34" t="n">
-        <v>4.889</v>
+        <v>5</v>
       </c>
       <c r="U34" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V34" t="n">
         <v>5</v>
       </c>
       <c r="W34" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X34" t="n">
         <v>0.5</v>
@@ -3763,16 +3763,16 @@
         <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>4</v>
+        <v>4.778</v>
       </c>
       <c r="U35" t="n">
-        <v>4.167</v>
+        <v>4.667</v>
       </c>
       <c r="V35" t="n">
-        <v>3.833</v>
+        <v>4.667</v>
       </c>
       <c r="W35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3858,16 +3858,16 @@
         <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>4.833</v>
+        <v>4.778</v>
       </c>
       <c r="U36" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V36" t="n">
-        <v>4.833</v>
+        <v>4.667</v>
       </c>
       <c r="W36" t="n">
-        <v>4.833</v>
+        <v>4.667</v>
       </c>
       <c r="X36" t="n">
         <v>0</v>
@@ -3953,16 +3953,16 @@
         <v>2</v>
       </c>
       <c r="T37" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="U37" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V37" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W37" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X37" t="n">
         <v>0</v>
@@ -4048,16 +4048,16 @@
         <v>2</v>
       </c>
       <c r="T38" t="n">
-        <v>4.666</v>
+        <v>4.778</v>
       </c>
       <c r="U38" t="n">
-        <v>4.333</v>
+        <v>4.667</v>
       </c>
       <c r="V38" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W38" t="n">
-        <v>4.833</v>
+        <v>4.667</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -4143,16 +4143,16 @@
         <v>2</v>
       </c>
       <c r="T39" t="n">
-        <v>4.778</v>
+        <v>4.667</v>
       </c>
       <c r="U39" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V39" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W39" t="n">
-        <v>4.667</v>
+        <v>4</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
@@ -4238,16 +4238,16 @@
         <v>2</v>
       </c>
       <c r="T40" t="n">
-        <v>4.889</v>
+        <v>5</v>
       </c>
       <c r="U40" t="n">
         <v>5</v>
       </c>
       <c r="V40" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W40" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X40" t="n">
         <v>0</v>
@@ -4333,16 +4333,16 @@
         <v>2</v>
       </c>
       <c r="T41" t="n">
-        <v>4.778</v>
+        <v>5</v>
       </c>
       <c r="U41" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="W41" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -4428,16 +4428,16 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>4.722</v>
+        <v>4.5</v>
       </c>
       <c r="U42" t="n">
         <v>4.833</v>
       </c>
       <c r="V42" t="n">
-        <v>4.833</v>
+        <v>4</v>
       </c>
       <c r="W42" t="n">
-        <v>4.5</v>
+        <v>4.667</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -4523,16 +4523,16 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>4.111</v>
+        <v>4.556</v>
       </c>
       <c r="U43" t="n">
-        <v>3.667</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>3.833</v>
+        <v>4.667</v>
       </c>
       <c r="W43" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X43" t="n">
         <v>0</v>
@@ -4618,16 +4618,16 @@
         <v>4</v>
       </c>
       <c r="T44" t="n">
-        <v>4.222</v>
+        <v>4.556</v>
       </c>
       <c r="U44" t="n">
-        <v>4.667</v>
+        <v>3.667</v>
       </c>
       <c r="V44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -4713,16 +4713,16 @@
         <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>3.889</v>
+        <v>4.722</v>
       </c>
       <c r="U45" t="n">
-        <v>3.167</v>
+        <v>4.667</v>
       </c>
       <c r="V45" t="n">
-        <v>4</v>
+        <v>4.833</v>
       </c>
       <c r="W45" t="n">
-        <v>4.5</v>
+        <v>4.667</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -4808,16 +4808,16 @@
         <v>2</v>
       </c>
       <c r="T46" t="n">
-        <v>3.889</v>
+        <v>4.611</v>
       </c>
       <c r="U46" t="n">
-        <v>4.167</v>
+        <v>4.667</v>
       </c>
       <c r="V46" t="n">
-        <v>3.333</v>
+        <v>4.5</v>
       </c>
       <c r="W46" t="n">
-        <v>4.167</v>
+        <v>4.667</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -4903,16 +4903,16 @@
         <v>2</v>
       </c>
       <c r="T47" t="n">
-        <v>4.056</v>
+        <v>4.389</v>
       </c>
       <c r="U47" t="n">
-        <v>3.667</v>
+        <v>4.667</v>
       </c>
       <c r="V47" t="n">
-        <v>4.667</v>
+        <v>4.5</v>
       </c>
       <c r="W47" t="n">
-        <v>3.833</v>
+        <v>4</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
@@ -4998,16 +4998,16 @@
         <v>2</v>
       </c>
       <c r="T48" t="n">
-        <v>4.611</v>
+        <v>4.278</v>
       </c>
       <c r="U48" t="n">
-        <v>4.167</v>
+        <v>5</v>
       </c>
       <c r="V48" t="n">
-        <v>4.833</v>
+        <v>3.833</v>
       </c>
       <c r="W48" t="n">
-        <v>4.833</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>0</v>
@@ -5093,16 +5093,16 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>3.389</v>
+        <v>3.667</v>
       </c>
       <c r="U49" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="V49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W49" t="n">
         <v>3.333</v>
-      </c>
-      <c r="V49" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="W49" t="n">
-        <v>3.5</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -5188,16 +5188,16 @@
         <v>2</v>
       </c>
       <c r="T50" t="n">
-        <v>3.944</v>
+        <v>4.167</v>
       </c>
       <c r="U50" t="n">
-        <v>4.5</v>
+        <v>4.667</v>
       </c>
       <c r="V50" t="n">
-        <v>3.333</v>
+        <v>4</v>
       </c>
       <c r="W50" t="n">
-        <v>4</v>
+        <v>3.833</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -5283,13 +5283,13 @@
         <v>2</v>
       </c>
       <c r="T51" t="n">
-        <v>4.5</v>
+        <v>4.278</v>
       </c>
       <c r="U51" t="n">
         <v>4.833</v>
       </c>
       <c r="V51" t="n">
-        <v>4.667</v>
+        <v>4</v>
       </c>
       <c r="W51" t="n">
         <v>4</v>
@@ -5378,7 +5378,7 @@
         <v>4</v>
       </c>
       <c r="T52" t="n">
-        <v>4.889</v>
+        <v>4.944</v>
       </c>
       <c r="U52" t="n">
         <v>4.833</v>
@@ -5387,7 +5387,7 @@
         <v>5</v>
       </c>
       <c r="W52" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X52" t="n">
         <v>0</v>
@@ -5473,16 +5473,16 @@
         <v>4</v>
       </c>
       <c r="T53" t="n">
-        <v>4.5</v>
+        <v>4.889</v>
       </c>
       <c r="U53" t="n">
-        <v>4</v>
+        <v>4.667</v>
       </c>
       <c r="V53" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="W53" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
@@ -5571,13 +5571,13 @@
         <v>4.667</v>
       </c>
       <c r="U54" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V54" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="W54" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X54" t="n">
         <v>0</v>
@@ -5663,16 +5663,16 @@
         <v>3</v>
       </c>
       <c r="T55" t="n">
-        <v>4.611</v>
+        <v>4.889</v>
       </c>
       <c r="U55" t="n">
-        <v>4.5</v>
+        <v>4.833</v>
       </c>
       <c r="V55" t="n">
         <v>4.833</v>
       </c>
       <c r="W55" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="X55" t="n">
         <v>0</v>
@@ -5758,13 +5758,13 @@
         <v>3</v>
       </c>
       <c r="T56" t="n">
-        <v>4.778</v>
+        <v>4.889</v>
       </c>
       <c r="U56" t="n">
         <v>4.667</v>
       </c>
       <c r="V56" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="W56" t="n">
         <v>5</v>
@@ -5853,16 +5853,16 @@
         <v>2</v>
       </c>
       <c r="T57" t="n">
-        <v>4.222</v>
+        <v>4.778</v>
       </c>
       <c r="U57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V57" t="n">
-        <v>4.167</v>
+        <v>4.667</v>
       </c>
       <c r="W57" t="n">
-        <v>4.5</v>
+        <v>4.667</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -5948,13 +5948,13 @@
         <v>2</v>
       </c>
       <c r="T58" t="n">
-        <v>4.667</v>
+        <v>4.556</v>
       </c>
       <c r="U58" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="V58" t="n">
-        <v>4.667</v>
+        <v>4</v>
       </c>
       <c r="W58" t="n">
         <v>4.667</v>
@@ -6043,16 +6043,16 @@
         <v>2</v>
       </c>
       <c r="T59" t="n">
-        <v>4.889</v>
+        <v>4.778</v>
       </c>
       <c r="U59" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="V59" t="n">
-        <v>5</v>
+        <v>4.333</v>
       </c>
       <c r="W59" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X59" t="n">
         <v>0</v>
@@ -6138,16 +6138,16 @@
         <v>3</v>
       </c>
       <c r="T60" t="n">
-        <v>4.333</v>
+        <v>4.556</v>
       </c>
       <c r="U60" t="n">
         <v>4</v>
       </c>
       <c r="V60" t="n">
-        <v>4.167</v>
+        <v>4.667</v>
       </c>
       <c r="W60" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X60" t="n">
         <v>0</v>
@@ -6233,16 +6233,16 @@
         <v>2</v>
       </c>
       <c r="T61" t="n">
+        <v>4.889</v>
+      </c>
+      <c r="U61" t="n">
         <v>4.667</v>
       </c>
-      <c r="U61" t="n">
-        <v>4.5</v>
-      </c>
       <c r="V61" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="W61" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X61" t="n">
         <v>0</v>
@@ -6328,13 +6328,13 @@
         <v>4</v>
       </c>
       <c r="T62" t="n">
-        <v>4.055</v>
+        <v>4.389</v>
       </c>
       <c r="U62" t="n">
+        <v>4.833</v>
+      </c>
+      <c r="V62" t="n">
         <v>4.333</v>
-      </c>
-      <c r="V62" t="n">
-        <v>3.833</v>
       </c>
       <c r="W62" t="n">
         <v>4</v>
@@ -6423,16 +6423,16 @@
         <v>3</v>
       </c>
       <c r="T63" t="n">
-        <v>4.556</v>
+        <v>4.944</v>
       </c>
       <c r="U63" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="V63" t="n">
-        <v>4.5</v>
+        <v>4.833</v>
       </c>
       <c r="W63" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="X63" t="n">
         <v>0</v>
@@ -6518,16 +6518,16 @@
         <v>4</v>
       </c>
       <c r="T64" t="n">
-        <v>4.389</v>
+        <v>4.778</v>
       </c>
       <c r="U64" t="n">
-        <v>4.167</v>
+        <v>4.833</v>
       </c>
       <c r="V64" t="n">
         <v>4.5</v>
       </c>
       <c r="W64" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="X64" t="n">
         <v>0</v>
@@ -6613,16 +6613,16 @@
         <v>4</v>
       </c>
       <c r="T65" t="n">
-        <v>4.556</v>
+        <v>4.611</v>
       </c>
       <c r="U65" t="n">
-        <v>4.333</v>
+        <v>4</v>
       </c>
       <c r="V65" t="n">
-        <v>4.667</v>
+        <v>4.833</v>
       </c>
       <c r="W65" t="n">
-        <v>4.667</v>
+        <v>5</v>
       </c>
       <c r="X65" t="n">
         <v>0</v>
@@ -6711,10 +6711,10 @@
         <v>4.556</v>
       </c>
       <c r="U66" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="V66" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="W66" t="n">
         <v>4.667</v>
@@ -6803,16 +6803,16 @@
         <v>2</v>
       </c>
       <c r="T67" t="n">
-        <v>4.5</v>
+        <v>4.889</v>
       </c>
       <c r="U67" t="n">
+        <v>5</v>
+      </c>
+      <c r="V67" t="n">
+        <v>5</v>
+      </c>
+      <c r="W67" t="n">
         <v>4.667</v>
-      </c>
-      <c r="V67" t="n">
-        <v>4</v>
-      </c>
-      <c r="W67" t="n">
-        <v>4.833</v>
       </c>
       <c r="X67" t="n">
         <v>0</v>
@@ -6898,16 +6898,16 @@
         <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>4.389</v>
+        <v>4.778</v>
       </c>
       <c r="U68" t="n">
         <v>4.667</v>
       </c>
       <c r="V68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="W68" t="n">
-        <v>4.5</v>
+        <v>4.667</v>
       </c>
       <c r="X68" t="n">
         <v>0</v>
@@ -6993,16 +6993,16 @@
         <v>2</v>
       </c>
       <c r="T69" t="n">
-        <v>4.333</v>
+        <v>4.944</v>
       </c>
       <c r="U69" t="n">
-        <v>4.333</v>
+        <v>4.833</v>
       </c>
       <c r="V69" t="n">
-        <v>3.833</v>
+        <v>5</v>
       </c>
       <c r="W69" t="n">
-        <v>4.833</v>
+        <v>5</v>
       </c>
       <c r="X69" t="n">
         <v>0</v>
@@ -7088,16 +7088,16 @@
         <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>3.778</v>
+        <v>4.167</v>
       </c>
       <c r="U70" t="n">
-        <v>3.333</v>
+        <v>4.5</v>
       </c>
       <c r="V70" t="n">
-        <v>3.667</v>
+        <v>3.5</v>
       </c>
       <c r="W70" t="n">
-        <v>4.333</v>
+        <v>4.5</v>
       </c>
       <c r="X70" t="n">
         <v>0</v>
@@ -7183,16 +7183,16 @@
         <v>2</v>
       </c>
       <c r="T71" t="n">
-        <v>4.167</v>
+        <v>4.389</v>
       </c>
       <c r="U71" t="n">
-        <v>4</v>
+        <v>4.667</v>
       </c>
       <c r="V71" t="n">
-        <v>4.167</v>
+        <v>4</v>
       </c>
       <c r="W71" t="n">
-        <v>4.333</v>
+        <v>4.5</v>
       </c>
       <c r="X71" t="n">
         <v>0</v>
